--- a/MO_year1_awardees.xlsx
+++ b/MO_year1_awardees.xlsx
@@ -416,7 +416,7 @@
     <t xml:space="preserve">RHTP_AWARD_PASS_THROUGH</t>
   </si>
   <si>
-    <t xml:space="preserve">RCJ's $6,500,000 matches DSS's 'around $6.5M'. It is in this file, as a PASS_THROUGH_UNRESOLVED to rural EMS agencies MEMSA has not named -- not a hospital dollar.</t>
+    <t xml:space="preserve">RCJ's $6,500,000 matches DSS's 'around $6.5M'. It is in this file, as a PASS_THROUGH_UNRESOLVED to rural EMS agencies MEMSA has not named -- not a hospital dollar. WHETHER MEMSA HAS NAMED THEM IS UNKNOWN, NOT NO: https://memsa.org/rht-funding/ answers HTTP 202 with a /.well-known/sgcaptcha/ interstitial, re-tested 2026-09-01 and unchanged. It is NOT a user-agent question -- all four of (project honest (+url), RFC Mozilla/5.0 (compatible), bare Mozilla/5.0, full Chrome) get 202, so §3's michigan.gov exception would not help; robots.txt is itself 202, so no crawler policy is on offer; and the gate needs JavaScript, not a header. Nor is there an archive route: archive.org's availability API answers 200 and returns no snapshot at all, so web.archive.org being unreachable (blocker 7) is not what is in the way -- there is nothing behind it. DO NOT RE-LITIGATE THIS unless testing it deliberately. If it ever answers 200, MEMSA's sub-awardees are a real extraction and still not hospital dollars: DSS states the eligible class and it is rural EMS agencies.</t>
   </si>
   <si>
     <t xml:space="preserve">Missouri Doula Association -- a real award, RCJ's amount short</t>
